--- a/Docs/QA/Onedow.xlsx
+++ b/Docs/QA/Onedow.xlsx
@@ -9190,7 +9190,7 @@
         </x:is>
       </x:c>
       <x:c r="G3" s="48" t="str">
-        <x:v>작업 상태 (2026-09-29)</x:v>
+        <x:v>작업 상태 (2026-10-07)</x:v>
       </x:c>
       <x:c r="H3" s="48" t="str">
         <x:v>검토 메모 · 현행 소스 대조</x:v>
@@ -9222,10 +9222,10 @@
         </x:is>
       </x:c>
       <x:c r="G4" s="43" t="str">
-        <x:v>미작업 · UI 후속</x:v>
+        <x:v>Clear · 스모크 PASS (2026-10-06)</x:v>
       </x:c>
       <x:c r="H4" s="43" t="str">
-        <x:v>배경 블러/정렬 개선 요청입니다. 별도 UI 개선 단계로 남아 있습니다.</x:v>
+        <x:v>설정 옵션 칸을 행 단위 균등 폭·가운데 정렬로 통일해 켜짐/꺼짐 간격이 다른 토글과 같아졌습니다. KR/EN 확인 — build/smoke/qaS2</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="60" customHeight="1">
@@ -9254,10 +9254,10 @@
         </x:is>
       </x:c>
       <x:c r="G5" s="43" t="str">
-        <x:v>미작업 · UI 후속</x:v>
+        <x:v>Clear · 스모크 PASS (2026-10-06)</x:v>
       </x:c>
       <x:c r="H5" s="43" t="str">
-        <x:v>FPS 옵션 간격 개선 요청입니다.</x:v>
+        <x:v>FPS 6개 옵션을 가장 넓은 라벨 기준 균등 칸으로 바꿔 간격이 일정해졌습니다. KR/EN 확인 — build/smoke/qaS2</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="60" customHeight="1">
@@ -9286,10 +9286,10 @@
         </x:is>
       </x:c>
       <x:c r="G6" s="43" t="str">
-        <x:v>미해결 · Medium</x:v>
+        <x:v>Clear · 스모크 PASS (2026-10-06)</x:v>
       </x:c>
       <x:c r="H6" s="43" t="str">
-        <x:v>설정 슬라이더/뒤로/저장 기준선 불일치 보고입니다.</x:v>
+        <x:v>볼륨 값 '100' 폭을 측정해 슬라이더 길이를 줄이고 값을 컨트롤 열 오른쪽 끝에 맞췄습니다(스크롤 레일 침범 해소). 뒤로/변경 저장은 같은 기준선 확인 — build/smoke/qaC</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="123.75" customHeight="1">
@@ -9318,10 +9318,10 @@
         </x:is>
       </x:c>
       <x:c r="G7" s="43" t="str">
-        <x:v>미해결 · Medium</x:v>
+        <x:v>Clear · 스모크 PASS (2026-10-06)</x:v>
       </x:c>
       <x:c r="H7" s="43" t="str">
-        <x:v>중요 팝업 텍스트 정렬 문제 보고입니다.</x:v>
+        <x:v>증강 선택 카드의 [n] 키와 이름을 줄 높이 중앙이 아닌 같은 기준선에 맞췄습니다. KR/EN/JP 확인 — build/smoke/qaC2, qaR</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="82.5" customHeight="1">
@@ -9350,10 +9350,10 @@
         </x:is>
       </x:c>
       <x:c r="G8" s="43" t="str">
-        <x:v>미해결 · Medium</x:v>
+        <x:v>Clear · 스모크 PASS (2026-10-06)</x:v>
       </x:c>
       <x:c r="H8" s="43" t="str">
-        <x:v>증강 패널 강조 표시 정렬 문제 보고입니다.</x:v>
+        <x:v>보유 증강 행 강조 막대와 호버 판정을 글자 줄 위아래 같은 여백으로 맞췄습니다 — build/smoke/qaC2</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="90" customHeight="1">
@@ -9412,10 +9412,10 @@
         </x:is>
       </x:c>
       <x:c r="G10" s="43" t="str">
-        <x:v>미해결 · High</x:v>
+        <x:v>Clear · 스모크 PASS (2026-10-06)</x:v>
       </x:c>
       <x:c r="H10" s="43" t="str">
-        <x:v>게임 오버 제목/탭/카운트 겹침 보고입니다.</x:v>
+        <x:v>보유 코인 라벨이 '보유 별자리'로 잘못 표기되던 것을 '보유 코인'으로 정정하고, 숫자 글리프 높이 기준으로 위치를 계산해 획득 코인 값과 겹치지 않게 했습니다. KR/EN/JP 확인 — build/smoke/qa07</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="87" customHeight="1">
@@ -9442,10 +9442,10 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="G11" s="43" t="str">
-        <x:v>코드 수정 · 화면 검증 대기</x:v>
+        <x:v>Clear · 스모크 PASS (2026-10-06)</x:v>
       </x:c>
       <x:c r="H11" s="43" t="str">
-        <x:v>증강 상세 패널에서 제목·수치·설명 위치를 실제 글꼴 높이 기준으로 계산하고 본문을 패널 폭에 맞춰 줄바꿈하도록 조정했습니다. Release 빌드 확인 완료; 인게임 간격 확인 전에는 Clear로 처리하지 않았습니다.</x:v>
+        <x:v>증강 상세 패널 제목·수치·설명 간격 정상 확인 — build/smoke/qa21b</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="164.25" customHeight="1">
@@ -9474,10 +9474,10 @@
         </x:is>
       </x:c>
       <x:c r="G12" s="43" t="str">
-        <x:v>확인 필요 · Medium</x:v>
+        <x:v>Clear · 수동 확인 PASS (2026-10-06)</x:v>
       </x:c>
       <x:c r="H12" s="43" t="str">
-        <x:v>Codex 아이콘/텍스트 위치 보고입니다. 게임 화면 재확인 필요.</x:v>
+        <x:v>스모크(입력 활성 상태)에서 게임 화면 내 아이콘·라벨 밀림 없음 확인 후, 사용자가 실제 한글 IME 조합 입력을 녹화로 검증해 정상 동작을 확인했습니다(2026-10-06 13:49 녹화). 코드 변경 없음 — build/smoke/qa09</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="92.25" customHeight="1">
@@ -9504,10 +9504,10 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="G13" s="43" t="str">
-        <x:v>코드 수정 · 입력 검증 대기</x:v>
+        <x:v>Clear · 스모크 PASS (2026-10-06)</x:v>
       </x:c>
       <x:c r="H13" s="43" t="str">
-        <x:v>일시정지 메뉴의 호버 판정을 애니메이션/호버 이동 후 화면에 그리는 버튼 좌표와 맞추고, 인접 항목 간 패딩을 줄였습니다. Release 빌드 확인 완료; 인게임 포인터 검증 전에는 Clear로 처리하지 않았습니다.</x:v>
+        <x:v>재개/설정 경계 부근 3지점에 포인터를 두어 동시 호버가 발생하지 않음을 확인했습니다 — build/smoke/qa10</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="79.5" customHeight="1">
@@ -9596,10 +9596,10 @@
         </x:is>
       </x:c>
       <x:c r="G16" s="43" t="str">
-        <x:v>미작업 · UI 후속</x:v>
+        <x:v>Clear · 스모크 PASS (2026-10-06)</x:v>
       </x:c>
       <x:c r="H16" s="43" t="str">
-        <x:v>상점 메타 상세 패널 위치 개선 요청입니다.</x:v>
+        <x:v>선택 모듈이 놓이는 별자리 중심을 화면 30%→45%로 옮기고, 상세 패널을 좁히고 내려 레일 라벨과 겹치지 않게 했습니다. KR/EN 확인 — build/smoke/qa13</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="165" customHeight="1">
@@ -9628,10 +9628,10 @@
         </x:is>
       </x:c>
       <x:c r="G17" s="43" t="str">
-        <x:v>텍스트 역할 수정 · 화면 검증 대기</x:v>
+        <x:v>Clear · 스모크 PASS (2026-10-06)</x:v>
       </x:c>
       <x:c r="H17" s="43" t="str">
-        <x:v>카테고리명은 부제목 36px, 좌측 하위 설정 목록은 설명 20px, 상세 항목명과 일반 값은 제목 40px, 켜짐/꺼짐 토글은 부제목 36px로 조정했습니다. 우측 패널의 카테고리 머리말과 설정명·값 묶음은 글꼴 높이를 기준으로 상하 중앙 정렬했습니다. Release 빌드는 통과했습니다. 아코디언 동작 및 실제 화면 검증이 남아 있어 Clear로 처리하지 않았습니다.</x:v>
+        <x:v>제목·부제 겹침 없음, 현재 카테고리만 펼쳐지고 호버한 카테고리(소리)가 펼쳐지는 것을 확인했습니다 — build/smoke/qaS2</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="165" customHeight="1">
@@ -9660,10 +9660,10 @@
         </x:is>
       </x:c>
       <x:c r="G18" s="43" t="str">
-        <x:v>미작업 · UI 후속</x:v>
+        <x:v>Clear · 스모크 PASS (2026-10-06)</x:v>
       </x:c>
       <x:c r="H18" s="43" t="str">
-        <x:v>Codex 상세 정보 위치 개선 요청입니다.</x:v>
+        <x:v>현재 빌드에서 선택 엔티티가 화면 중앙(약 50%)에 배치됨을 확인했습니다. 코드 변경 없음 — build/smoke/qaB</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="126" customHeight="1">
@@ -9692,10 +9692,10 @@
         </x:is>
       </x:c>
       <x:c r="G19" s="43" t="str">
-        <x:v>미해결</x:v>
+        <x:v>Clear · 스모크 PASS (2026-10-06)</x:v>
       </x:c>
       <x:c r="H19" s="43" t="str">
-        <x:v>무기 선택 제목 안티앨리어싱 문제로 기록되어 있습니다.</x:v>
+        <x:v>133px로 구운 XL 글꼴을 크게 축소해 그리던 것을 L 글꼴로 바꿔 계단 현상을 없앴습니다 — build/smoke/qaA</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="165" customHeight="1">
@@ -9724,10 +9724,10 @@
         </x:is>
       </x:c>
       <x:c r="G20" s="43" t="str">
-        <x:v>미작업 · UI 후속</x:v>
+        <x:v>Clear · 스모크 PASS (2026-10-06)</x:v>
       </x:c>
       <x:c r="H20" s="43" t="str">
-        <x:v>Trial 헤더/무한 스크롤 개선 요청입니다.</x:v>
+        <x:v>'0/4 활성'을 제목과 같은 글꼴·크기·기준선으로 통일하고 긴 제목일 때 간격을 보장했습니다. JP 표기 '有効' 추가. 목록 스크롤은 이미 끝에서 멈추는 유한 스크롤임을 확인 — build/smoke/qa17, qa17b</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="72" customHeight="1">
@@ -9756,10 +9756,10 @@
         </x:is>
       </x:c>
       <x:c r="G21" s="43" t="str">
-        <x:v>미작업 · 문구</x:v>
+        <x:v>Clear · 스모크 PASS (2026-10-06)</x:v>
       </x:c>
       <x:c r="H21" s="43" t="str">
-        <x:v>“런”을 “플레이”로 변경하는 문구 요청입니다.</x:v>
+        <x:v>툴팁은 이미 '플레이 설정'으로 반영되어 있었고, 튜토리얼·도감에 남은 '런' 표기도 '플레이'로 정리했습니다 — build/smoke/qaA</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="165" customHeight="1">
@@ -9848,10 +9848,10 @@
         </x:is>
       </x:c>
       <x:c r="G24" s="43" t="str">
-        <x:v>미해결</x:v>
+        <x:v>Clear · 스모크 PASS (2026-10-06)</x:v>
       </x:c>
       <x:c r="H24" s="43" t="str">
-        <x:v>수정자 입력 줄바꿈 문제로 기록되어 있습니다.</x:v>
+        <x:v>줄바꿈 함수가 '-1.0/s'를 한 단어로 유지함을 확인했고, 설명문의 ' - ' 구분자를 ' · '로 바꿔 항목 단위로 줄이 나뉘게 했습니다 — build/smoke/qaB</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="60" customHeight="1">
@@ -9912,10 +9912,106 @@
         </x:is>
       </x:c>
       <x:c r="G26" s="43" t="str">
-        <x:v>미작업 · 문구</x:v>
+        <x:v>Clear · 스모크 PASS (2026-10-06)</x:v>
       </x:c>
       <x:c r="H26" s="43" t="str">
-        <x:v>구분 기호를 슬래시에서 가운데점으로 바꾸는 요청입니다.</x:v>
+        <x:v>지적된 '/' 구분 문자열은 이미 '·'로 바뀌어 있었고, 남은 ' - ' 구분자 9곳도 '·'로 통일했습니다</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="60" customHeight="1">
+      <x:c r="A27" s="27" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B27" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">textOverlap</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C27" s="29" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">도감 검색 — 검색 결과 없음 안내</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D27" s="30" t="n"/>
+      <x:c r="E27" s="29" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[스모크 발견] 검색 결과가 없을 때 '검색 결과 없음' 제목과 '다른 검색어를 입력하세요' 안내 문구가 겹쳐 표시됨</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F27" s="32" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Medium</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G27" s="43" t="str">
+        <x:v>Clear · 스모크 PASS (2026-10-06)</x:v>
+      </x:c>
+      <x:c r="H27" s="43" t="str">
+        <x:v>안내 문구 위치가 고정 오프셋(+62px)이라 Title 크기 제목과 겹쳤습니다. 제목 실측 높이 + 10px 아래에 배치하도록 수정했습니다. 수정 전 재현(build/smoke/qaEmpty) 후 KR/EN/JP 통과 확인(build/smoke/qaEmpty2). 관측체·모듈 탭 공용 코드</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="60" customHeight="1">
+      <x:c r="A28" s="27" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B28" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">textOverlap</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C28" s="29" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">도감 검색 — 해금 목록 헤더</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D28" s="30" t="n"/>
+      <x:c r="E28" s="29" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[회귀 스모크 발견] 검색 시 EN 'UNLOCK PROGRESS'와 '0 MATCHES'가 겹치고, 1280×720에서는 검색창 아래 조작 안내 줄이 제목에 붙음</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F28" s="32" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Medium</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G28" s="43" t="str">
+        <x:v>Clear · 스모크 PASS (2026-10-07)</x:v>
+      </x:c>
+      <x:c r="H28" s="43" t="str">
+        <x:v>결과 수 2자리 폭을 항상 예약해 제목 크기를 맞추고, 그래도 부족하면(작은 창) 결과 수를 검색창 안쪽 X 왼쪽으로 옮겼습니다. 제목 Y를 안내 줄 실측 높이 아래로 계산합니다. 기본/1600×900/1280×720 × KR/EN/JP 확인 — build/smoke/fix_*, final_*</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="60" customHeight="1">
+      <x:c r="A29" s="27" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B29" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">textOverlap</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C29" s="29" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">런 설정 — 활성 시련 상세 머리</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D29" s="30" t="n"/>
+      <x:c r="E29" s="29" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[회귀 스모크 발견] '드래그 이동 · 휠 스크롤' 안내가 '현재 적용 합계' 제목과 겹침(JP는 '0 / 4 ENABLED'와 겹침)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F29" s="32" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Medium</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G29" s="43" t="str">
+        <x:v>Clear · 스모크 PASS (2026-10-07)</x:v>
+      </x:c>
+      <x:c r="H29" s="43" t="str">
+        <x:v>안내를 '0 / 4 활성화' 줄 오른쪽(구분선 위)에 폭을 맞춰 배치하고, 자리가 없으면 상태 제목 줄로, 그래도 없으면 생략합니다. JP 문구를 'ドラッグ · ホイール'로 단축. 작은 창(1600×900 이하)에서는 생략됩니다 — build/smoke/fix3_*, final_*</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
